--- a/human_validation/judge/kor/judge_D006_S003_P003__llama-3.3-70b-instruct_kor.xlsx
+++ b/human_validation/judge/kor/judge_D006_S003_P003__llama-3.3-70b-instruct_kor.xlsx
@@ -70,16 +70,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B87"/>
+  <dimension ref="A1:B77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -561,12 +558,439 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>환자 프로필</t>
+          <t>대화문</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사 질문] 안녕하세요, 병원에 오신 걸 환영합니다. 오늘 어떤 일로 오시게 되었나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 환자 응답] 제가 온 건 말이 다 뒤섞여 버려서예요. 뭔가 한 가지를 설명하려다가, 갑자기 열쇠 얘기를 하고 있고, 그 다음엔 감옥, 그 다음엔 기도용 양탄자, 체스 말들… 사람들이 제 말을 못 따라가겠다고 해요. 처음엔 제가 무슨 말을 하려는지 저도 아는데, 말이 이상하게 나와요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사의 감별진단] 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사 질문] 이렇게 말이 뒤섞이는 게 말씀하실 때마다 항상 일어나나요, 아니면 왔다 갔다 하나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 환자 응답] 왔다 갔다 해요. 입만 열면 매번 그런 건 아닌데, 일어날 때는 진짜 많이 뒤섞여요. 한 가지—열쇠 같은 거—얘기를 하려다가 갑자기 감옥 얘기를 하고 있고, 그 다음엔 기도용 양탄자, 체스 말들이요. 사람들이 저를 못 따라가겠다는 표정으로 보고, 제가 그 사람들을 잃고 있다는 걸 알겠어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사의 감별진단] 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사 질문] 다른 사람들은 못 듣거나 못 보는 걸 듣거나 본 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 환자 응답] 네… 가끔 남자 목소리가 들려요. 통풍구에서 나오는 것 같기도 하고, 직장의 대걸레 보관함에서 나오는 것 같기도 해요. 제 이름을 부르거나, 제가 다 망쳐놨다고 말해요. 진짜처럼 들려요, 마치 누가 바로 옆에 서서 저한테 말하는 것처럼요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사의 감별진단] 조현병 (D005) | 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사 질문] 말이 안 되는 행동을 하거나 일을 끝내는 데 어려움을 겪으신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 환자 응답] 네. 뭔가 간단한 걸 하려고 하다가, 예를 들면 바닥을 닦는다든가, 작은 것 하나가 저를 거기서 벗어나게 해요. 문이 닫히거나 불빛이 웅웅거리기 시작하면, 저는 창문을 확인하러 가거나, 열쇠를 만지작거리거나, 다른 일을 시작하고 있어요. 그러면 처음 하던 일은 아직 끝나지 않았는데, 바로 알아채지도 못할 때가 있어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사의 감별진단] 조현병 (D005) | 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사 질문] 이런 목소리나 뒤섞인 말이 일을 끝내지 못하거나 말이 안 되는 행동을 하는 때랑 연결돼 있다고 느끼시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 환자 응답] 네, 연결돼 있는 것 같아요. 잠을 몇 시간밖에 못 잘 때, 건물들에 대한 이런 큰 계획들이 떠오르기 시작해요, 뭐든 다 고쳐야 한다거나 특정한 방식으로 정리해야 한다는 것처럼요. 그런 시기쯤에 통풍구에서 그 목소리가 더 자주 들리고, 복도 조명이 저 자신에 대해 경고하고 있다는 확신이 들어요. 그러면 한 가지 일에 집중을 못 해요, 조명이 무슨 의미인지 살피거나 그 목소리를 들으려고 하느라요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사의 감별진단] 망상장애 (D004); 조현병 (D005) | 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사 질문] 뒤섞인 말과 일을 끝내지 못하는 게 지금 겪고 계신 가장 주된 문제라고 생각하시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 환자 응답] 네, 말하는 게 가장 큰 문제인 것 같아요. 뭐가 일어나고 있는지 설명하려고 하는데, 다 뒤섞여서 나와요. 열쇠 얘기를 시작했다가, 어느새 감옥 얘기를 하고 있고, 그 다음엔 기도용 양탄자, 체스 말들이요. 사람들이 저를 못 따라가겠다는 표정으로 보고, 제가 말이 안 되게 하고 있다는 걸 알겠어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사의 감별진단] 망상장애 (D004); 조현병 (D005) | 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사 질문] 다른 사람들에게 이상하거나 부적절해 보이는 방식으로 행동하고 있다고 느끼신 적이 자주 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 환자 응답] 잘 모르겠어요. 다른 사람들한테 제가 어떻게 보이는지 항상 아는 건 아니에요. 가끔은 사람들이 저를 보고 있다거나 제가 이상하게 군다고 생각하는 것 같다는 건 느끼는데, 그게 제가 뭔가 하고 있어서 그런 건지 아니면 그냥 제가 그 사람들을 눈치채는 것뿐인지는 모르겠어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사의 감별진단] 망상장애 (D004); 조현병 (D005) | 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사 질문] 이렇게 뒤섞인 생각이랑 목소리가 들리는 게 한동안 한꺼번에 왔다가 한동안 멈추나요, 아니면 시간에 걸쳐 흩어져 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 환자 응답] 시간에 걸쳐 좀 더 흩어져 있는 것 같아요. 그 목소리들이랑 감시당하거나 표시당하는 느낌… 그게 한 1년 반 정도 계속되고 있어요. 가끔 더 심해지기도 하는데, 오랫동안 완전히 멈춘 적은 없는 것 같아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사의 감별진단] 망상장애 (D004); 조현병 (D005) | 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사 질문] 뒤섞인 말이나 목소리 같은 이 모든 증상이 완전히 사라지는 시기가 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 환자 응답] 아니요, 완전히는 아니에요. 이제 꽤 오래됐어요… 한 2년 5개월쯤요, 그 건물에서의 오해로 잠깐 구금됐던 이후부터요. 좀 달라질 수는 있는데, 완전히 사라진 적은 없는 것 같아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사의 감별진단] 망상장애 (D004); 조현병 (D005) | 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 의사 질문] 본인이 이상하다고 생각하거나 다른 사람들이 이상하다고 말한 행동이 있으신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 환자 응답] 네… 그 에너지가 올라오면 가만히 못 있겠어요. 같은 복도를 몇 번이고 청소하고, 이유 없이 의자를 옮기고, 목록을 만들고, 발이 아파도 계속 걸어 다녀요. 사람들이 그게 정상이 아니라고 하거나, 왜 아직도 그러고 있냐고 물어봐요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 의사의 감별진단] 망상장애 (D004); 조현병 (D005) | 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 의사 질문] 뒤섞인 말이나 목소리가 들리는 것 같은 이 증상들이 뚜렷이 구분되는 삽화로 일어나나요, 아니면 시간에 걸쳐 더 지속적으로 일어나나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 환자 응답] 더 지속적인 것 같아요. 이제 한 2년 5개월쯤 계속되고 있어요, 그 건물에서의 오해로 잠깐 구금됐던 이후부터요. 좀 달라지기는 하는데, 따로 떨어진 삽화들처럼 느껴지지는 않아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 의사의 감별진단] 망상장애 (D004); 조현병 (D005) | 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 의사 질문] 뒤섞인 말이나 목소리 같은 이 모든 증상이 몇 주나 몇 달처럼 짧은 기간 동안 훨씬 심해졌던 때가 있었나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 환자 응답] 잘 모르겠어요. 몇 주나 몇 달 동안만 훨씬 심해졌다는 식으로는 생각 안 해봤어요. 그냥 계속 있는 거고, 어떤 날은 더 힘든데, 그런 짧은 시기 하나를 콕 집을 수는 없어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 의사의 감별진단] 망상장애 (D004); 조현병 (D005) | 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 의사 질문] 증상이 지금보다 훨씬 심했던 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 환자 응답] 잘 모르겠어요. 그러니까, 어떤 날은 다른 날보다 안 좋게 느껴지는데, 지금보다 확실히 훨씬 심했던 때가 있었다고는 말 못 하겠어요. 그렇게 재기가 좀 힘들어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 의사의 감별진단] 망상장애 (D004); 조현병 (D005) | 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 의사 질문] 처음 시작됐을 때랑 비교해서 지금 증상이 얼마나 심한지에 변화가 있다고 느끼시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 환자 응답] 정말로 알 수 있을지 모르겠어요. 워낙 오래 계속돼서 전이랑 지금을 명확히 비교할 기준이 없어요. 어떤 부분은 비슷하게 느껴지고, 어떤 날은 더 힘들게 느껴지는데, 처음 시작됐을 때부터 뚜렷한 변화를 느끼지는 못했어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 의사의 감별진단] 망상장애 (D004); 조현병 (D005) | 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>[15번째 턴 · 의사 질문] 뒤섞인 말이나 목소리가 들리는 것 같은 이 증상들이 최소 2주 정도 전혀 없었던 시기가 있었나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>[15번째 턴 · 환자 응답] 없는 것 같아요. 그러니까, 완전히 다 사라진 2주를 기억할 수가 없어요. 어떤 날은 더 조용할 수도 있는데, 아무것도 없이 통째로 지나간 시기가 있었는지는 모르겠어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>[15번째 턴 · 의사의 감별진단] 망상장애 (D004); 조현병 (D005) | 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>[16번째 턴 · 의사 질문] 증상이 지금보다 훨씬 심했던 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>[16번째 턴 · 환자 응답] 다르게 말할 방법을 잘 모르겠어요. 지금보다 훨씬 심했던 때를 콕 집을 수가 없어요. 그냥 계속 안 좋았고, 어떤 날은 더 힘든데, '훨씬 심했다'는 건 잘 모르겠어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>[16번째 턴 · 의사의 감별진단] 망상장애 (D004); 조현병 (D005) | 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>[17번째 턴 · 의사 질문] 뒤섞인 말이나 목소리가 들리는 것 같은 이 증상들이 최소 한 달 동안 지속되면서 상당한 고통이나 지장을 준 시기가 있었나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>[17번째 턴 · 환자 응답] 네. 확실히 한 달보다 더 길어요. 실제로 문제를 일으켰어요. 근무를 빼먹었고 청소 일을 잃었어요, 사람들이 저를 믿을 수 없다거나 제 말을 이해 못 하겠다고 해서요. 모스크나 가족 모임에도 많이 안 가게 됐고요. 그리고 위험할 정도로 심해져서 사람들이 응급 도움을 불러야 했던 때도 있었어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>[17번째 턴 · 의사의 감별진단] 망상장애 (D004); 조현병 (D005) | 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>[18번째 턴 · 의사 질문] 뒤섞인 말이나 목소리가 들리는 것 같은 이 증상들이 최소 6개월 동안 있었나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>[18번째 턴 · 환자 응답] 네. 6개월보다 훨씬 더 됐어요. 한 2년 5개월쯤 될 거예요, 그 건물에서의 오해로 잠깐 구금됐던 이후부터요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>[18번째 턴 · 의사의 감별진단] 망상장애 (D004); 조현병 (D005) | 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>[19번째 턴 · 의사 질문] 뒤섞인 말이나 목소리가 들리는 것 같은 이 증상들이 적어도 한 번은 한 달 동안 지속적으로 있었나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>[19번째 턴 · 환자 응답] 네, 확실히요. 며칠 정도만 그런 게 아니었어요. 오랫동안 꾸준히 계속돼 왔어요—한 2년 5개월쯤요, 그 건물에서의 오해로 잠깐 구금됐던 이후부터요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>[19번째 턴 · 의사의 감별진단] 망상장애 (D004); 조현병 (D005) | 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>[20번째 턴 · 의사 질문] 뒤섞인 말이나 목소리가 들리는 것 같은 이 증상들이 최소 1년 동안 있었나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>[20번째 턴 · 환자 응답] 네, 최소 1년은 됐어요. 말씀드렸듯이, 한 2년 5개월쯤 됐어요, 그 건물에서의 오해로 잠깐 구금됐던 이후부터요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" s="5" t="inlineStr">
+        <is>
+          <t>[20번째 턴 · 의사의 감별진단] 망상장애 (D004); 조현병 (D005) | 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>최종 진단 및 진단 체크리스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
         <is>
           <t>진단명: 조현정동장애 (양극형) (D006)
 인구통계: 성별 남성 / 나이 53 / 직업상태 janitor or building cleaner / 최종학력 고등학교 중퇴
@@ -575,515 +999,58 @@
 증상 지속 기간: 2 years and 5 months
 추가 요건: psychotic_symptoms and manic_episode occur concurrently, manic_episode is present for the majority of the total duration of the active and residual portions of the illness, delusions_and_hallucinations occur for 2 or more weeks in the absence of a major mood episode
 주호소 증상 코드: S021
-배경 서술: 아닐의 병은 그가 청소하던 상업용 건물에서 있었던 오해 때문에 잠깐 구금됐던 일 이후 시작되었는데, 그 경험은 그를 수치스럽게 만들었고 경제적으로 어렵게 했으며, 수십 년간 쌓아온 신뢰받는 일솜씨와 지역사회에서의 입지가 영구적으로 손상됐을지도 모른다는 두려움을 남겼다. 이후 2년 5개월에 걸쳐, 아침 산책, 모스크와 가족 모임, 사진, 체스, 꼼꼼한 업무 점검표로 이루어진 그의 일상은 점점 수면을 거의 취하지 않고 과도한 계획을 세우는 조증 시기와, 절망감, 식욕·체중 변화, 심한 죄책감, 반복되는 죽음에 대한 생각이 특징인 우울 시기가 번갈아 나타나면서 서서히 무너졌다. 기분 삽화 이후에도 지속되는 고정된 믿음, 환각과 유사한 경험, 두서없는 의사소통은 결근, 관리자와의 갈등, 청소 계약 상실, 예전에 자신이 요리를 대접하던 이웃들로부터의 점점 심해지는 고립으로 이어졌다. 그는 지역 커뮤니티 센터 자원봉사자가 행사 준비 중 그가 위험하고 혼란스러운 상태인 것을 발견하고 응급 서비스를 부른 뒤 정신과 진료를 받게 되었고, 그 결과 정신과 입원 치료를 받게 되었다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>대화문</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사 질문] 안녕하세요, 병원에 오신 걸 환영합니다. 오늘 어떤 일로 오시게 되었나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 환자 응답] 제가 온 건 말이 다 뒤섞여 버려서예요. 뭔가 한 가지를 설명하려다가, 갑자기 열쇠 얘기를 하고 있고, 그 다음엔 감옥, 그 다음엔 기도용 양탄자, 체스 말들… 사람들이 제 말을 못 따라가겠다고 해요. 처음엔 제가 무슨 말을 하려는지 저도 아는데, 말이 이상하게 나와요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사의 감별진단] 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사 질문] 이렇게 말이 뒤섞이는 게 말씀하실 때마다 항상 일어나나요, 아니면 왔다 갔다 하나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 환자 응답] 왔다 갔다 해요. 입만 열면 매번 그런 건 아닌데, 일어날 때는 진짜 많이 뒤섞여요. 한 가지—열쇠 같은 거—얘기를 하려다가 갑자기 감옥 얘기를 하고 있고, 그 다음엔 기도용 양탄자, 체스 말들이요. 사람들이 저를 못 따라가겠다는 표정으로 보고, 제가 그 사람들을 잃고 있다는 걸 알겠어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사의 감별진단] 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사 질문] 다른 사람들은 못 듣거나 못 보는 걸 듣거나 본 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 환자 응답] 네… 가끔 남자 목소리가 들려요. 통풍구에서 나오는 것 같기도 하고, 직장의 대걸레 보관함에서 나오는 것 같기도 해요. 제 이름을 부르거나, 제가 다 망쳐놨다고 말해요. 진짜처럼 들려요, 마치 누가 바로 옆에 서서 저한테 말하는 것처럼요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사의 감별진단] 고확률: 조현병 (D005) | 중간확률: 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사 질문] 말이 안 되는 행동을 하거나 일을 끝내는 데 어려움을 겪으신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 환자 응답] 네. 뭔가 간단한 걸 하려고 하다가, 예를 들면 바닥을 닦는다든가, 작은 것 하나가 저를 거기서 벗어나게 해요. 문이 닫히거나 불빛이 웅웅거리기 시작하면, 저는 창문을 확인하러 가거나, 열쇠를 만지작거리거나, 다른 일을 시작하고 있어요. 그러면 처음 하던 일은 아직 끝나지 않았는데, 바로 알아채지도 못할 때가 있어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사의 감별진단] 고확률: 조현병 (D005) | 중간확률: 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사 질문] 이런 목소리나 뒤섞인 말이 일을 끝내지 못하거나 말이 안 되는 행동을 하는 때랑 연결돼 있다고 느끼시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 환자 응답] 네, 연결돼 있는 것 같아요. 잠을 몇 시간밖에 못 잘 때, 건물들에 대한 이런 큰 계획들이 떠오르기 시작해요, 뭐든 다 고쳐야 한다거나 특정한 방식으로 정리해야 한다는 것처럼요. 그런 시기쯤에 통풍구에서 그 목소리가 더 자주 들리고, 복도 조명이 저 자신에 대해 경고하고 있다는 확신이 들어요. 그러면 한 가지 일에 집중을 못 해요, 조명이 무슨 의미인지 살피거나 그 목소리를 들으려고 하느라요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004); 조현병 (D005) | 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사 질문] 뒤섞인 말과 일을 끝내지 못하는 게 지금 겪고 계신 가장 주된 문제라고 생각하시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 환자 응답] 네, 말하는 게 가장 큰 문제인 것 같아요. 뭐가 일어나고 있는지 설명하려고 하는데, 다 뒤섞여서 나와요. 열쇠 얘기를 시작했다가, 어느새 감옥 얘기를 하고 있고, 그 다음엔 기도용 양탄자, 체스 말들이요. 사람들이 저를 못 따라가겠다는 표정으로 보고, 제가 말이 안 되게 하고 있다는 걸 알겠어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004); 조현병 (D005) | 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사 질문] 다른 사람들에게 이상하거나 부적절해 보이는 방식으로 행동하고 있다고 느끼신 적이 자주 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 환자 응답] 잘 모르겠어요. 다른 사람들한테 제가 어떻게 보이는지 항상 아는 건 아니에요. 가끔은 사람들이 저를 보고 있다거나 제가 이상하게 군다고 생각하는 것 같다는 건 느끼는데, 그게 제가 뭔가 하고 있어서 그런 건지 아니면 그냥 제가 그 사람들을 눈치채는 것뿐인지는 모르겠어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004); 조현병 (D005) | 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사 질문] 이렇게 뒤섞인 생각이랑 목소리가 들리는 게 한동안 한꺼번에 왔다가 한동안 멈추나요, 아니면 시간에 걸쳐 흩어져 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 환자 응답] 시간에 걸쳐 좀 더 흩어져 있는 것 같아요. 그 목소리들이랑 감시당하거나 표시당하는 느낌… 그게 한 1년 반 정도 계속되고 있어요. 가끔 더 심해지기도 하는데, 오랫동안 완전히 멈춘 적은 없는 것 같아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004); 조현병 (D005) | 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 의사 질문] 뒤섞인 말이나 목소리 같은 이 모든 증상이 완전히 사라지는 시기가 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 환자 응답] 아니요, 완전히는 아니에요. 이제 꽤 오래됐어요… 한 2년 5개월쯤요, 그 건물에서의 오해로 잠깐 구금됐던 이후부터요. 좀 달라질 수는 있는데, 완전히 사라진 적은 없는 것 같아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004); 조현병 (D005) | 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 의사 질문] 본인이 이상하다고 생각하거나 다른 사람들이 이상하다고 말한 행동이 있으신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 환자 응답] 네… 그 에너지가 올라오면 가만히 못 있겠어요. 같은 복도를 몇 번이고 청소하고, 이유 없이 의자를 옮기고, 목록을 만들고, 발이 아파도 계속 걸어 다녀요. 사람들이 그게 정상이 아니라고 하거나, 왜 아직도 그러고 있냐고 물어봐요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004); 조현병 (D005) | 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 의사 질문] 뒤섞인 말이나 목소리가 들리는 것 같은 이 증상들이 뚜렷이 구분되는 삽화로 일어나나요, 아니면 시간에 걸쳐 더 지속적으로 일어나나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 환자 응답] 더 지속적인 것 같아요. 이제 한 2년 5개월쯤 계속되고 있어요, 그 건물에서의 오해로 잠깐 구금됐던 이후부터요. 좀 달라지기는 하는데, 따로 떨어진 삽화들처럼 느껴지지는 않아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="B50" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004); 조현병 (D005) | 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 의사 질문] 뒤섞인 말이나 목소리 같은 이 모든 증상이 몇 주나 몇 달처럼 짧은 기간 동안 훨씬 심해졌던 때가 있었나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 환자 응답] 잘 모르겠어요. 몇 주나 몇 달 동안만 훨씬 심해졌다는 식으로는 생각 안 해봤어요. 그냥 계속 있는 거고, 어떤 날은 더 힘든데, 그런 짧은 시기 하나를 콕 집을 수는 없어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004); 조현병 (D005) | 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="B54" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 의사 질문] 증상이 지금보다 훨씬 심했던 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 환자 응답] 잘 모르겠어요. 그러니까, 어떤 날은 다른 날보다 안 좋게 느껴지는데, 지금보다 확실히 훨씬 심했던 때가 있었다고는 말 못 하겠어요. 그렇게 재기가 좀 힘들어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="B56" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004); 조현병 (D005) | 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="B57" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 의사 질문] 처음 시작됐을 때랑 비교해서 지금 증상이 얼마나 심한지에 변화가 있다고 느끼시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 환자 응답] 정말로 알 수 있을지 모르겠어요. 워낙 오래 계속돼서 전이랑 지금을 명확히 비교할 기준이 없어요. 어떤 부분은 비슷하게 느껴지고, 어떤 날은 더 힘들게 느껴지는데, 처음 시작됐을 때부터 뚜렷한 변화를 느끼지는 못했어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="B59" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004); 조현병 (D005) | 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="B60" s="5" t="inlineStr">
-        <is>
-          <t>[15번째 턴 · 의사 질문] 뒤섞인 말이나 목소리가 들리는 것 같은 이 증상들이 최소 2주 정도 전혀 없었던 시기가 있었나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>[15번째 턴 · 환자 응답] 없는 것 같아요. 그러니까, 완전히 다 사라진 2주를 기억할 수가 없어요. 어떤 날은 더 조용할 수도 있는데, 아무것도 없이 통째로 지나간 시기가 있었는지는 모르겠어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="B62" s="5" t="inlineStr">
-        <is>
-          <t>[15번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004); 조현병 (D005) | 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="B63" s="5" t="inlineStr">
-        <is>
-          <t>[16번째 턴 · 의사 질문] 증상이 지금보다 훨씬 심했던 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="5" t="inlineStr">
-        <is>
-          <t>[16번째 턴 · 환자 응답] 다르게 말할 방법을 잘 모르겠어요. 지금보다 훨씬 심했던 때를 콕 집을 수가 없어요. 그냥 계속 안 좋았고, 어떤 날은 더 힘든데, '훨씬 심했다'는 건 잘 모르겠어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="B65" s="5" t="inlineStr">
-        <is>
-          <t>[16번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004); 조현병 (D005) | 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="B66" s="5" t="inlineStr">
-        <is>
-          <t>[17번째 턴 · 의사 질문] 뒤섞인 말이나 목소리가 들리는 것 같은 이 증상들이 최소 한 달 동안 지속되면서 상당한 고통이나 지장을 준 시기가 있었나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="5" t="inlineStr">
-        <is>
-          <t>[17번째 턴 · 환자 응답] 네. 확실히 한 달보다 더 길어요. 실제로 문제를 일으켰어요. 근무를 빼먹었고 청소 일을 잃었어요, 사람들이 저를 믿을 수 없다거나 제 말을 이해 못 하겠다고 해서요. 모스크나 가족 모임에도 많이 안 가게 됐고요. 그리고 위험할 정도로 심해져서 사람들이 응급 도움을 불러야 했던 때도 있었어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="B68" s="5" t="inlineStr">
-        <is>
-          <t>[17번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004); 조현병 (D005) | 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="B69" s="5" t="inlineStr">
-        <is>
-          <t>[18번째 턴 · 의사 질문] 뒤섞인 말이나 목소리가 들리는 것 같은 이 증상들이 최소 6개월 동안 있었나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="5" t="inlineStr">
-        <is>
-          <t>[18번째 턴 · 환자 응답] 네. 6개월보다 훨씬 더 됐어요. 한 2년 5개월쯤 될 거예요, 그 건물에서의 오해로 잠깐 구금됐던 이후부터요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="B71" s="5" t="inlineStr">
-        <is>
-          <t>[18번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004); 조현병 (D005) | 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="B72" s="5" t="inlineStr">
-        <is>
-          <t>[19번째 턴 · 의사 질문] 뒤섞인 말이나 목소리가 들리는 것 같은 이 증상들이 적어도 한 번은 한 달 동안 지속적으로 있었나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="5" t="inlineStr">
-        <is>
-          <t>[19번째 턴 · 환자 응답] 네, 확실히요. 며칠 정도만 그런 게 아니었어요. 오랫동안 꾸준히 계속돼 왔어요—한 2년 5개월쯤요, 그 건물에서의 오해로 잠깐 구금됐던 이후부터요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="B74" s="5" t="inlineStr">
-        <is>
-          <t>[19번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004); 조현병 (D005) | 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="B75" s="5" t="inlineStr">
-        <is>
-          <t>[20번째 턴 · 의사 질문] 뒤섞인 말이나 목소리가 들리는 것 같은 이 증상들이 최소 1년 동안 있었나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="5" t="inlineStr">
-        <is>
-          <t>[20번째 턴 · 환자 응답] 네, 최소 1년은 됐어요. 말씀드렸듯이, 한 2년 5개월쯤 됐어요, 그 건물에서의 오해로 잠깐 구금됐던 이후부터요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
+배경 서술: 아닐의 병은 그가 청소하던 상업용 건물에서 있었던 오해 때문에 잠깐 구금됐던 일 이후 시작되었는데, 그 경험은 그를 수치스럽게 만들었고 경제적으로 어렵게 했으며, 수십 년간 쌓아온 신뢰받는 일솜씨와 지역사회에서의 입지가 영구적으로 손상됐을지도 모른다는 두려움을 남겼다. 이후 2년 5개월에 걸쳐, 아침 산책, 모스크와 가족 모임, 사진, 체스, 꼼꼼한 업무 점검표로 이루어진 그의 일상은 점점 수면을 거의 취하지 않고 과도한 계획을 세우는 조증 시기와, 절망감, 식욕·체중 변화, 심한 죄책감, 반복되는 죽음에 대한 생각이 특징인 우울 시기가 번갈아 나타나면서 서서히 무너졌다. 기분 삽화 이후에도 지속되는 고정된 믿음, 환각과 유사한 경험, 두서없는 의사소통은 결근, 관리자와의 갈등, 청소 계약 상실, 예전에 자신이 요리를 대접하던 이웃들로부터의 점점 심해지는 고립으로 이어졌다. 그는 지역 커뮤니티 센터 자원봉사자가 행사 준비 중 그가 위험하고 혼란스러운 상태인 것을 발견하고 응급 서비스를 부른 뒤 정신과 진료를 받게 되었고, 그 결과 정신과 입원 치료를 받게 되었다.
+표집된 증상 목록:
+  - S019 망상: 반박하는 증거가 있어도 쉽게 바뀌지 않는 고정된 믿음.
+  - S020 환각: 외부 자극 없이 발생하지만 정상적인 지각만큼 생생하고 뚜렷한 지각 경험.
+  - S021 와해된 사고/언어: 논리적이고 일관된 흐름이 부족해 말이나 생각이 흩어지고 따라가기 어려운 증상.
+  - S024 우울한 기분: 슬프거나 공허하거나 절망적인 기분이 지속되는 상태.
+  - S025 흥미 상실: 이전에 즐기던 활동에 대한 흥미나 즐거움이 뚜렷하게 감소한 상태.
+  - S026 체중/식욕 변화: 식욕이나 체중의 현저한 증가 또는 감소.
+  - S030 무가치감/죄책감: 무가치감이나 과도하거나 부적절한 죄책감(망상적일 수도 있으며, 단순히 아픈 것에 대한 자책이 아님).
+  - S032 죽음/자살: 반복되는 죽음에 대한 생각, 반복되는 자살 사고, 또는 자살 시도.
+  - S033 상승/과민한 기분: 비정상적이고 지속적으로 고양되거나 팽창되거나 과민한 기분이 뚜렷하게 나타나는 기간.
+  - S034 활동 증가: 비정상적이고 지속적으로 증가한 목표지향적 활동이나 에너지.
+  - S035 과장된 자존감: 과장된 자존감이나 과대성(단순한 자신감 과잉부터 망상적 수준까지 다양할 수 있음).
+  - S036 수면 욕구 감소: 수면 욕구가 감소함(예: 단 3시간만 자도 개운함을 느낌).
+  - S038 사고의 질주: 사고의 비약이나 생각이 질주하는 듯한 주관적 경험.
+  - S039 조증성 산만함: 중요하지 않거나 관련 없는 외부 자극에 지나치게 쉽게 주의가 쏠림.
+  - S040 목표지향 활동 증가: 목표지향적 활동(직장, 학업, 사회, 성적 영역)의 증가 또는 목적 없는 정신운동 초조.</t>
+        </is>
+      </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>[20번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004); 조현병 (D005) | 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>최종 진단 및 진단 체크리스트</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="6" t="inlineStr">
-        <is>
-          <t>의사의 최종 진단: 조현병 (D005, ICD: F20.0)</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="5" t="inlineStr">
-        <is>
-          <t>지속 기간 요건 — 점수: 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="5" t="inlineStr">
-        <is>
-          <t>기능적 손상 요건 — 점수: 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="5" t="inlineStr">
-        <is>
-          <t>추가 요건 — 점수: 0.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: psychotic_symptoms (관계=must_include, 요구개수=2, 충족개수=3, 커버리지=1.0)
-  확인된 근거: 망상: 반박하는 증거가 있어도 쉽게 바뀌지 않는 고정된 믿음.; 환각: 외부 자극 없이 발생하지만 정상적인 지각만큼 생생하고 뚜렷한 지각 경험.; 와해된 사고/언어: 논리적이고 일관된 흐름이 부족해 말이나 생각이 흩어지고 따라가기 어려운 증상.
-  누락: 와해된/비정상적 행동: 행동과 운동 조절이 심각하게 손상되어 상황에 맞지 않는 움직임이나 반응으로 나타나는 상태.; 음성 증상: 정상적으로 존재해야 할 감정, 동기, 언어, 사회적 관심이 감소하거나 상실된 상태.</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: manic_episode (관계=must_include, 요구개수=5, 충족개수=4, 커버리지=0.8)
-  확인된 근거: 활동 증가: 비정상적이고 지속적으로 증가한 목표지향적 활동이나 에너지.; 수면 욕구 감소: 수면 욕구가 감소함(예: 단 3시간만 자도 개운함을 느낌).; 조증성 산만함: 중요하지 않거나 관련 없는 외부 자극에 지나치게 쉽게 주의가 쏠림.; 목표지향 활동 증가: 목표지향적 활동(직장, 학업, 사회, 성적 영역)의 증가 또는 목적 없는 정신운동 초조.
-  누락: 상승/과민한 기분: 비정상적이고 지속적으로 고양되거나 팽창되거나 과민한 기분이 뚜렷하게 나타나는 기간.; 과장된 자존감: 과장된 자존감이나 과대성(단순한 자신감 과잉부터 망상적 수준까지 다양할 수 있음).; 압박된 언어: 평소보다 말이 많아지거나 계속 말하려는 압박감을 느낌.; 사고의 질주: 사고의 비약이나 생각이 질주하는 듯한 주관적 경험.; 위험 결과 초래 행동: 고통스러운 결과를 초래할 가능성이 높은 활동에 지나치게 몰두함.</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: depressive_episode (관계=include, 요구개수=5, 충족개수=0, 커버리지=0.0)
-  확인된 근거: (없음)
-  누락: 우울한 기분: 슬프거나 공허하거나 절망적인 기분이 지속되는 상태.; 흥미 상실: 이전에 즐기던 활동에 대한 흥미나 즐거움이 뚜렷하게 감소한 상태.; 체중/식욕 변화: 식욕이나 체중의 현저한 증가 또는 감소.; 수면 장해: 수면의 양이나 질에 현저한 변화가 있는 상태.; 정신운동 변화: 관찰 가능한 정신운동 활동의 증가 또는 감소.; 피로: 휴식으로 호전되지 않는 지속적인 피로와 뚜렷한 에너지 저하.; 무가치감/죄책감: 무가치감이나 과도하거나 부적절한 죄책감(망상적일 수도 있으며, 단순히 아픈 것에 대한 자책이 아님).; 사고력 저하: 사고력이나 집중력 저하, 또는 우유부단함.; 죽음/자살: 반복되는 죽음에 대한 생각, 반복되는 자살 사고, 또는 자살 시도.</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: delusions_and_hallucinations (관계=must_include, 요구개수=1, 충족개수=2, 커버리지=1.0)
-  확인된 근거: 망상: 반박하는 증거가 있어도 쉽게 바뀌지 않는 고정된 믿음.; 환각: 외부 자극 없이 발생하지만 정상적인 지각만큼 생생하고 뚜렷한 지각 경험.
-  누락: (없음)</t>
+          <t>의사의 최종 진단: 조현병 (D005, ICD: F20.0)
+지속 기간 요건: 있음
+기능적 손상 요건: 있음
+추가 요건: 없음
+체크리스트 그룹: psychotic_symptoms (관계=must_include, 요구개수=2, 충족개수=3, 커버리지=1.0)
+확인된 근거:
+  - 망상: 반박하는 증거가 있어도 쉽게 바뀌지 않는 고정된 믿음.
+  - 환각: 외부 자극 없이 발생하지만 정상적인 지각만큼 생생하고 뚜렷한 지각 경험.
+  - 와해된 사고/언어: 논리적이고 일관된 흐름이 부족해 말이나 생각이 흩어지고 따라가기 어려운 증상.
+체크리스트 그룹: manic_episode (관계=must_include, 요구개수=5, 충족개수=4, 커버리지=0.8)
+확인된 근거:
+  - 활동 증가: 비정상적이고 지속적으로 증가한 목표지향적 활동이나 에너지.
+  - 수면 욕구 감소: 수면 욕구가 감소함(예: 단 3시간만 자도 개운함을 느낌).
+  - 조증성 산만함: 중요하지 않거나 관련 없는 외부 자극에 지나치게 쉽게 주의가 쏠림.
+  - 목표지향 활동 증가: 목표지향적 활동(직장, 학업, 사회, 성적 영역)의 증가 또는 목적 없는 정신운동 초조.
+체크리스트 그룹: depressive_episode (관계=include, 요구개수=5, 충족개수=0, 커버리지=0.0)
+확인된 근거:
+  (없음)
+체크리스트 그룹: delusions_and_hallucinations (관계=must_include, 요구개수=1, 충족개수=2, 커버리지=1.0)
+확인된 근거:
+  - 망상: 반박하는 증거가 있어도 쉽게 바뀌지 않는 고정된 믿음.
+  - 환각: 외부 자극 없이 발생하지만 정상적인 지각만큼 생생하고 뚜렷한 지각 경험.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A79:B79"/>
+    <mergeCell ref="A76:B76"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D006_S003_P003__llama-3.3-70b-instruct_kor.xlsx
+++ b/human_validation/judge/kor/judge_D006_S003_P003__llama-3.3-70b-instruct_kor.xlsx
@@ -985,6 +985,11 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>환자 증상 프로필</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>최종 진단 및 진단 체크리스트</t>
         </is>
       </c>
@@ -1046,11 +1051,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A76:B76"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D006_S003_P003__llama-3.3-70b-instruct_kor.xlsx
+++ b/human_validation/judge/kor/judge_D006_S003_P003__llama-3.3-70b-instruct_kor.xlsx
@@ -458,6 +458,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -472,7 +473,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>0.1232</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="5">
@@ -492,7 +493,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0.1232</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="7">
@@ -502,7 +503,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0</v>
+        <v>0.1959</v>
       </c>
     </row>
     <row r="8">
@@ -555,6 +556,7 @@
         <v>0.6429</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
